--- a/sampleprojects/TaxReturn/excel/states/MD.xlsx
+++ b/sampleprojects/TaxReturn/excel/states/MD.xlsx
@@ -83,7 +83,7 @@
     <t>MFJ/QSS: $5,150 std ded, 5.75%</t>
   </si>
   <si>
-    <t>set result.computed_state_taxable_income = the maximum of (result.agi - 5150.0) and 0.0; set result.computed_state_tax = result.computed_state_taxable_income * 0.0575</t>
+    <t>set result.computed_state_taxable_income = the maximum of (result.state_calc_agi - 5150.0) and 0.0; set result.computed_state_tax = result.computed_state_taxable_income * 0.0575</t>
   </si>
   <si>
     <t>X</t>
@@ -92,7 +92,7 @@
     <t>HOH: $2,550 std ded, 5.75%</t>
   </si>
   <si>
-    <t>set result.computed_state_taxable_income = the maximum of (result.agi - 2550.0) and 0.0; set result.computed_state_tax = result.computed_state_taxable_income * 0.0575</t>
+    <t>set result.computed_state_taxable_income = the maximum of (result.state_calc_agi - 2550.0) and 0.0; set result.computed_state_tax = result.computed_state_taxable_income * 0.0575</t>
   </si>
   <si>
     <t>Default (Single/MFS): $2,550 std ded, 5.75%</t>

--- a/sampleprojects/TaxReturn/excel/states/MD.xlsx
+++ b/sampleprojects/TaxReturn/excel/states/MD.xlsx
@@ -8,14 +8,15 @@
   </bookViews>
   <sheets>
     <sheet name="MD Tax" sheetId="2" r:id="rId4"/>
-    <sheet name="EDD" sheetId="3" r:id="rId6"/>
+    <sheet name="MD Military Retirement Subtract" sheetId="3" r:id="rId6"/>
+    <sheet name="EDD" sheetId="4" r:id="rId7"/>
   </sheets>
   <calcPr calcId="122211"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="135">
   <si>
     <t>DT: MD Tax</t>
   </si>
@@ -44,7 +45,7 @@
     <t/>
   </si>
   <si>
-    <t>set result.computed_state_tax = 0; set result.computed_state_taxable_income = 0; add "  Maryland Tax Calculation (top marginal 5.75%)" to job.audit_trail</t>
+    <t>set result.computed_state_tax = 0; set result.computed_state_taxable_income = 0; add "  Maryland Tax Calculation (top marginal 5.75%)" to job.audit_trail; set result.md_military_retirement_subtraction = 0.0; perform MD_Military_Retirement_Subtraction; add "  MD Form 502SU code u military retirement subtraction: $" + result.md_military_retirement_subtraction to job.audit_trail</t>
   </si>
   <si>
     <t>CONDITIONS: COMMENTS</t>
@@ -83,7 +84,7 @@
     <t>MFJ/QSS: $5,150 std ded, 5.75%</t>
   </si>
   <si>
-    <t>set result.computed_state_taxable_income = the maximum of (result.state_calc_agi - 5150.0) and 0.0; set result.computed_state_tax = result.computed_state_taxable_income * 0.0575</t>
+    <t>set result.computed_state_taxable_income = the maximum of (result.state_calc_agi - result.md_military_retirement_subtraction - 5150.0) and 0.0; set result.computed_state_tax = result.computed_state_taxable_income * 0.0575</t>
   </si>
   <si>
     <t>X</t>
@@ -92,7 +93,7 @@
     <t>HOH: $2,550 std ded, 5.75%</t>
   </si>
   <si>
-    <t>set result.computed_state_taxable_income = the maximum of (result.state_calc_agi - 2550.0) and 0.0; set result.computed_state_tax = result.computed_state_taxable_income * 0.0575</t>
+    <t>set result.computed_state_taxable_income = the maximum of (result.state_calc_agi - result.md_military_retirement_subtraction - 2550.0) and 0.0; set result.computed_state_tax = result.computed_state_taxable_income * 0.0575</t>
   </si>
   <si>
     <t>Default (Single/MFS): $2,550 std ded, 5.75%</t>
@@ -113,6 +114,51 @@
     <t>MD Single/MFS: 5.75% x max(AGI - $2,550, 0) per Md. Code, Tax-Gen. § 10-105</t>
   </si>
   <si>
+    <t>DT: MD Military Retirement Subtraction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COMMENTS: </t>
+  </si>
+  <si>
+    <t>TABLE_NUMBER: 52413</t>
+  </si>
+  <si>
+    <t>for all taxpayers</t>
+  </si>
+  <si>
+    <t>The taxpayer has military retirement income</t>
+  </si>
+  <si>
+    <t>taxpayer.military_retirement_pay &gt; 0</t>
+  </si>
+  <si>
+    <t>At least 55 on the last day of the taxable year</t>
+  </si>
+  <si>
+    <t>job.tax_year - (get yearof taxpayer.date_of_birth) &gt;= 55</t>
+  </si>
+  <si>
+    <t>Form 502SU code u: up to $20,000 at 55 and over</t>
+  </si>
+  <si>
+    <t>add the minimum of taxpayer.military_retirement_pay and md_military_retirement_exemption_55_plus to result.md_military_retirement_subtraction</t>
+  </si>
+  <si>
+    <t>Form 502SU code u: up to $12,500 under 55</t>
+  </si>
+  <si>
+    <t>add the minimum of taxpayer.military_retirement_pay and md_military_retirement_exemption_under_55 to result.md_military_retirement_subtraction</t>
+  </si>
+  <si>
+    <t>Military retirement income subtraction, Form 502SU code u: up to $20,000 for an individual at least 55 on the last day of the year (2025 Resident Booklet, Instruction 13; Tax-General 10-207(q)).</t>
+  </si>
+  <si>
+    <t>Form 502SU code u: up to $12,500 for an individual under 55.</t>
+  </si>
+  <si>
+    <t>No military retirement income for this taxpayer.</t>
+  </si>
+  <si>
     <t>EDD: EDD</t>
   </si>
   <si>
@@ -158,7 +204,7 @@
     <t>result</t>
   </si>
   <si>
-    <t>(23 attributes)</t>
+    <t>(24 attributes)</t>
   </si>
   <si>
     <t>md_bracket_1_limit</t>
@@ -308,7 +354,7 @@
     <t>20000.0</t>
   </si>
   <si>
-    <t>MD military retirement exemption amount for age 55+ (2025). Source: MOAA State Report Card</t>
+    <t>MD Form 502SU code u cap for an individual at least 55 years of age on the last day of the taxable year: $20,000 (2025 Resident Booklet, Instruction 13).</t>
   </si>
   <si>
     <t>md_military_retirement_exemption_under_55</t>
@@ -317,13 +363,22 @@
     <t>12500.0</t>
   </si>
   <si>
-    <t>MD military retirement exemption amount for under age 55 (2025). Source: MOAA State Report Card</t>
+    <t>MD Form 502SU code u cap for an individual under 55 on the last day of the taxable year: $12,500 (2025 Resident Booklet, Instruction 13).</t>
+  </si>
+  <si>
+    <t>md_military_retirement_subtraction</t>
+  </si>
+  <si>
+    <t>0.0</t>
+  </si>
+  <si>
+    <t>rw</t>
+  </si>
+  <si>
+    <t>Maryland Form 502SU code u, military retirement income: up to $20,000 for an individual at least 55 on the last day of the year, up to $12,500 under 55 (2025 Resident Booklet, Instruction 13). Computed per taxpayer by MD_Military_Retirement_Subtraction (#1330).</t>
   </si>
   <si>
     <t>md_military_retirement_taxable</t>
-  </si>
-  <si>
-    <t>0.0</t>
   </si>
   <si>
     <t>MD taxable military retirement after exemption (computed)</t>
@@ -1653,6 +1708,786 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
   <cols>
+    <col customWidth="true" max="1" min="1" width="20"/>
+    <col customWidth="true" max="3" min="2" width="40"/>
+    <col customWidth="true" max="19" min="4" width="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
+      <c r="O1" s="2"/>
+      <c r="P1" s="2"/>
+      <c r="Q1" s="2"/>
+      <c r="R1" s="2"/>
+      <c r="S1" s="2"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
+      <c r="O2" s="3"/>
+      <c r="P2" s="3"/>
+      <c r="Q2" s="3"/>
+      <c r="R2" s="3"/>
+      <c r="S2" s="3"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2"/>
+      <c r="N3" s="2"/>
+      <c r="O3" s="2"/>
+      <c r="P3" s="2"/>
+      <c r="Q3" s="2"/>
+      <c r="R3" s="2"/>
+      <c r="S3" s="2"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2"/>
+      <c r="N4" s="2"/>
+      <c r="O4" s="2"/>
+      <c r="P4" s="2"/>
+      <c r="Q4" s="2"/>
+      <c r="R4" s="2"/>
+      <c r="S4" s="2"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
+      <c r="N6" s="1"/>
+      <c r="O6" s="1"/>
+      <c r="P6" s="1"/>
+      <c r="Q6" s="1"/>
+      <c r="R6" s="1"/>
+      <c r="S6" s="1"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="5">
+        <v>1</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="3"/>
+      <c r="K7" s="3"/>
+      <c r="L7" s="3"/>
+      <c r="M7" s="3"/>
+      <c r="N7" s="3"/>
+      <c r="O7" s="3"/>
+      <c r="P7" s="3"/>
+      <c r="Q7" s="3"/>
+      <c r="R7" s="3"/>
+      <c r="S7" s="3"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1"/>
+      <c r="J9" s="1"/>
+      <c r="K9" s="1"/>
+      <c r="L9" s="1"/>
+      <c r="M9" s="1"/>
+      <c r="N9" s="1"/>
+      <c r="O9" s="1"/>
+      <c r="P9" s="1"/>
+      <c r="Q9" s="1"/>
+      <c r="R9" s="1"/>
+      <c r="S9" s="1"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D11" s="1">
+        <v>1</v>
+      </c>
+      <c r="E11" s="1">
+        <v>2</v>
+      </c>
+      <c r="F11" s="1">
+        <v>3</v>
+      </c>
+      <c r="G11" s="1">
+        <v>4</v>
+      </c>
+      <c r="H11" s="1">
+        <v>5</v>
+      </c>
+      <c r="I11" s="1">
+        <v>6</v>
+      </c>
+      <c r="J11" s="1">
+        <v>7</v>
+      </c>
+      <c r="K11" s="1">
+        <v>8</v>
+      </c>
+      <c r="L11" s="1">
+        <v>9</v>
+      </c>
+      <c r="M11" s="1">
+        <v>10</v>
+      </c>
+      <c r="N11" s="1">
+        <v>11</v>
+      </c>
+      <c r="O11" s="1">
+        <v>12</v>
+      </c>
+      <c r="P11" s="1">
+        <v>13</v>
+      </c>
+      <c r="Q11" s="1">
+        <v>14</v>
+      </c>
+      <c r="R11" s="1">
+        <v>15</v>
+      </c>
+      <c r="S11" s="1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5">
+        <v>1</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S12" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5">
+        <v>2</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S13" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B15" s="1"/>
+      <c r="C15" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="4">
+        <v>1</v>
+      </c>
+      <c r="E15" s="4">
+        <v>2</v>
+      </c>
+      <c r="F15" s="4">
+        <v>3</v>
+      </c>
+      <c r="G15" s="4">
+        <v>4</v>
+      </c>
+      <c r="H15" s="4">
+        <v>5</v>
+      </c>
+      <c r="I15" s="4">
+        <v>6</v>
+      </c>
+      <c r="J15" s="4">
+        <v>7</v>
+      </c>
+      <c r="K15" s="4">
+        <v>8</v>
+      </c>
+      <c r="L15" s="4">
+        <v>9</v>
+      </c>
+      <c r="M15" s="4">
+        <v>10</v>
+      </c>
+      <c r="N15" s="4">
+        <v>11</v>
+      </c>
+      <c r="O15" s="4">
+        <v>12</v>
+      </c>
+      <c r="P15" s="4">
+        <v>13</v>
+      </c>
+      <c r="Q15" s="4">
+        <v>14</v>
+      </c>
+      <c r="R15" s="4">
+        <v>15</v>
+      </c>
+      <c r="S15" s="4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5">
+        <v>1</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S16" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5">
+        <v>2</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S17" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B19" s="1"/>
+      <c r="C19" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D19" s="1">
+        <v>1</v>
+      </c>
+      <c r="E19" s="1">
+        <v>2</v>
+      </c>
+      <c r="F19" s="1">
+        <v>3</v>
+      </c>
+      <c r="G19" s="1">
+        <v>4</v>
+      </c>
+      <c r="H19" s="1">
+        <v>5</v>
+      </c>
+      <c r="I19" s="1">
+        <v>6</v>
+      </c>
+      <c r="J19" s="1">
+        <v>7</v>
+      </c>
+      <c r="K19" s="1">
+        <v>8</v>
+      </c>
+      <c r="L19" s="1">
+        <v>9</v>
+      </c>
+      <c r="M19" s="1">
+        <v>10</v>
+      </c>
+      <c r="N19" s="1">
+        <v>11</v>
+      </c>
+      <c r="O19" s="1">
+        <v>12</v>
+      </c>
+      <c r="P19" s="1">
+        <v>13</v>
+      </c>
+      <c r="Q19" s="1">
+        <v>14</v>
+      </c>
+      <c r="R19" s="1">
+        <v>15</v>
+      </c>
+      <c r="S19" s="1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5">
+        <v>1</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S20" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5">
+        <v>2</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S21" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5">
+        <v>3</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S22" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="12">
+    <mergeCell ref="A1:S1"/>
+    <mergeCell ref="A2:S2"/>
+    <mergeCell ref="A3:S3"/>
+    <mergeCell ref="A4:S4"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C6:S6"/>
+    <mergeCell ref="C7:S7"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="C9:S9"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A19:B19"/>
+  </mergeCells>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <cols>
     <col customWidth="true" max="1" min="1" width="18"/>
     <col customWidth="true" max="2" min="2" width="25"/>
     <col customWidth="true" max="3" min="3" width="10"/>
@@ -1669,56 +2504,56 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="s">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="C3" s="6"/>
       <c r="D3" s="6"/>
@@ -1737,25 +2572,25 @@
         <v>8</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="F4" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="H4" s="16" t="s">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="I4" s="7" t="s">
         <v>8</v>
@@ -1778,25 +2613,25 @@
         <v>8</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="D5" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="F5" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="H5" s="16" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="I5" s="8" t="s">
         <v>8</v>
@@ -1819,25 +2654,25 @@
         <v>8</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="F6" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="H6" s="16" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="I6" s="7" t="s">
         <v>8</v>
@@ -1860,25 +2695,25 @@
         <v>8</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="D7" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="F7" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="H7" s="16" t="s">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="I7" s="8" t="s">
         <v>8</v>
@@ -1901,25 +2736,25 @@
         <v>8</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="F8" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="H8" s="16" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="I8" s="7" t="s">
         <v>8</v>
@@ -1942,25 +2777,25 @@
         <v>8</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="D9" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E9" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="G9" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="F9" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="G9" s="8" t="s">
-        <v>51</v>
-      </c>
       <c r="H9" s="16" t="s">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="I9" s="8" t="s">
         <v>8</v>
@@ -1983,25 +2818,25 @@
         <v>8</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="D10" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>69</v>
+        <v>84</v>
       </c>
       <c r="F10" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="H10" s="16" t="s">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="I10" s="7" t="s">
         <v>8</v>
@@ -2024,25 +2859,25 @@
         <v>8</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>71</v>
+        <v>86</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="D11" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>72</v>
+        <v>87</v>
       </c>
       <c r="F11" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="H11" s="16" t="s">
-        <v>73</v>
+        <v>88</v>
       </c>
       <c r="I11" s="8" t="s">
         <v>8</v>
@@ -2065,25 +2900,25 @@
         <v>8</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>74</v>
+        <v>89</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="F12" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="H12" s="16" t="s">
-        <v>76</v>
+        <v>91</v>
       </c>
       <c r="I12" s="7" t="s">
         <v>8</v>
@@ -2106,25 +2941,25 @@
         <v>8</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="D13" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>78</v>
+        <v>93</v>
       </c>
       <c r="F13" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="H13" s="16" t="s">
-        <v>79</v>
+        <v>94</v>
       </c>
       <c r="I13" s="8" t="s">
         <v>8</v>
@@ -2147,25 +2982,25 @@
         <v>8</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="D14" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="F14" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="H14" s="16" t="s">
-        <v>82</v>
+        <v>97</v>
       </c>
       <c r="I14" s="7" t="s">
         <v>8</v>
@@ -2188,25 +3023,25 @@
         <v>8</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="D15" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="F15" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="H15" s="16" t="s">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="I15" s="8" t="s">
         <v>8</v>
@@ -2229,25 +3064,25 @@
         <v>8</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>86</v>
+        <v>101</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="D16" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>87</v>
+        <v>102</v>
       </c>
       <c r="F16" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="H16" s="16" t="s">
-        <v>88</v>
+        <v>103</v>
       </c>
       <c r="I16" s="7" t="s">
         <v>8</v>
@@ -2270,25 +3105,25 @@
         <v>8</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>89</v>
+        <v>104</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="D17" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="F17" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="H17" s="16" t="s">
-        <v>91</v>
+        <v>106</v>
       </c>
       <c r="I17" s="8" t="s">
         <v>8</v>
@@ -2311,25 +3146,25 @@
         <v>8</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>92</v>
+        <v>107</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="D18" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>93</v>
+        <v>108</v>
       </c>
       <c r="F18" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="H18" s="16" t="s">
-        <v>94</v>
+        <v>109</v>
       </c>
       <c r="I18" s="7" t="s">
         <v>8</v>
@@ -2352,25 +3187,25 @@
         <v>8</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="D19" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>96</v>
+        <v>111</v>
       </c>
       <c r="F19" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="H19" s="16" t="s">
-        <v>97</v>
+        <v>112</v>
       </c>
       <c r="I19" s="8" t="s">
         <v>8</v>
@@ -2393,25 +3228,25 @@
         <v>8</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>98</v>
+        <v>113</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="D20" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>99</v>
+        <v>114</v>
       </c>
       <c r="F20" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="H20" s="16" t="s">
-        <v>100</v>
+        <v>115</v>
       </c>
       <c r="I20" s="7" t="s">
         <v>8</v>
@@ -2434,25 +3269,25 @@
         <v>8</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>101</v>
+        <v>116</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="D21" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
       <c r="F21" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>51</v>
+        <v>118</v>
       </c>
       <c r="H21" s="16" t="s">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="I21" s="8" t="s">
         <v>8</v>
@@ -2475,25 +3310,25 @@
         <v>8</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="D22" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="F22" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="H22" s="16" t="s">
-        <v>106</v>
+        <v>121</v>
       </c>
       <c r="I22" s="7" t="s">
         <v>8</v>
@@ -2516,25 +3351,25 @@
         <v>8</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>107</v>
+        <v>122</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="D23" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>108</v>
+        <v>123</v>
       </c>
       <c r="F23" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="H23" s="16" t="s">
-        <v>109</v>
+        <v>124</v>
       </c>
       <c r="I23" s="8" t="s">
         <v>8</v>
@@ -2557,25 +3392,25 @@
         <v>8</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>110</v>
+        <v>125</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="D24" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>111</v>
+        <v>126</v>
       </c>
       <c r="F24" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G24" s="7" t="s">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="H24" s="16" t="s">
-        <v>112</v>
+        <v>127</v>
       </c>
       <c r="I24" s="7" t="s">
         <v>8</v>
@@ -2598,25 +3433,25 @@
         <v>8</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>113</v>
+        <v>128</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="D25" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>108</v>
+        <v>129</v>
       </c>
       <c r="F25" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G25" s="8" t="s">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="H25" s="16" t="s">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="I25" s="8" t="s">
         <v>8</v>
@@ -2639,25 +3474,25 @@
         <v>8</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>115</v>
+        <v>131</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="D26" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>108</v>
+        <v>126</v>
       </c>
       <c r="F26" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G26" s="7" t="s">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="H26" s="16" t="s">
-        <v>116</v>
+        <v>132</v>
       </c>
       <c r="I26" s="7" t="s">
         <v>8</v>
@@ -2672,6 +3507,47 @@
         <v>8</v>
       </c>
       <c r="M26" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B27" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="C27" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="D27" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E27" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="F27" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="G27" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="H27" s="16" t="s">
+        <v>134</v>
+      </c>
+      <c r="I27" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="J27" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="K27" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="L27" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="M27" s="8" t="s">
         <v>8</v>
       </c>
     </row>

--- a/sampleprojects/TaxReturn/excel/states/MD.xlsx
+++ b/sampleprojects/TaxReturn/excel/states/MD.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="138">
   <si>
     <t>DT: MD Tax</t>
   </si>
@@ -138,6 +138,12 @@
     <t>job.tax_year - (get yearof taxpayer.date_of_birth) &gt;= 55</t>
   </si>
   <si>
+    <t>Full-year resident entry only. A part-year or nonresident entry's income is built from the income entities, so the pension is not in it, and 4 U.S.C. 114 bars a state from taxing a nonresident's retirement income (#1330 review).</t>
+  </si>
+  <si>
+    <t>result.state_calc_resident_status is equal to "full_year"</t>
+  </si>
+  <si>
     <t>Form 502SU code u: up to $20,000 at 55 and over</t>
   </si>
   <si>
@@ -157,6 +163,9 @@
   </si>
   <si>
     <t>No military retirement income for this taxpayer.</t>
+  </si>
+  <si>
+    <t>Not a full-year resident entry: the pension is not in this entry's sourced income (the roster builds it from the income entities) and 4 U.S.C. 114 bars taxing a nonresident's retirement income, so nothing is subtracted.</t>
   </si>
   <si>
     <t>EDD: EDD</t>
@@ -1959,7 +1968,7 @@
         <v>15</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>8</v>
@@ -2018,7 +2027,7 @@
         <v>18</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>8</v>
@@ -2057,125 +2066,125 @@
         <v>8</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="1" t="s">
+    <row r="14">
+      <c r="A14" s="5">
+        <v>3</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S14" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B15" s="1"/>
-      <c r="C15" s="1" t="s">
+      <c r="B16" s="1"/>
+      <c r="C16" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="4">
+      <c r="D16" s="4">
         <v>1</v>
       </c>
-      <c r="E15" s="4">
+      <c r="E16" s="4">
         <v>2</v>
       </c>
-      <c r="F15" s="4">
+      <c r="F16" s="4">
         <v>3</v>
       </c>
-      <c r="G15" s="4">
+      <c r="G16" s="4">
         <v>4</v>
       </c>
-      <c r="H15" s="4">
+      <c r="H16" s="4">
         <v>5</v>
       </c>
-      <c r="I15" s="4">
+      <c r="I16" s="4">
         <v>6</v>
       </c>
-      <c r="J15" s="4">
+      <c r="J16" s="4">
         <v>7</v>
       </c>
-      <c r="K15" s="4">
-        <v>8</v>
-      </c>
-      <c r="L15" s="4">
+      <c r="K16" s="4">
+        <v>8</v>
+      </c>
+      <c r="L16" s="4">
         <v>9</v>
       </c>
-      <c r="M15" s="4">
+      <c r="M16" s="4">
         <v>10</v>
       </c>
-      <c r="N15" s="4">
+      <c r="N16" s="4">
         <v>11</v>
       </c>
-      <c r="O15" s="4">
+      <c r="O16" s="4">
         <v>12</v>
       </c>
-      <c r="P15" s="4">
+      <c r="P16" s="4">
         <v>13</v>
       </c>
-      <c r="Q15" s="4">
+      <c r="Q16" s="4">
         <v>14</v>
       </c>
-      <c r="R15" s="4">
+      <c r="R16" s="4">
         <v>15</v>
       </c>
-      <c r="S15" s="4">
+      <c r="S16" s="4">
         <v>16</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="5">
-        <v>1</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="J16" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="K16" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="L16" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="M16" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="N16" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="O16" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="P16" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q16" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="R16" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="S16" s="2" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>42</v>
@@ -2184,176 +2193,176 @@
         <v>43</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="E17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S17" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5">
+        <v>2</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="F17" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="J17" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="K17" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="L17" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="M17" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="N17" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="O17" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="P17" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q17" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="R17" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="S17" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="s">
+      <c r="F18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S18" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B19" s="1"/>
-      <c r="C19" s="1" t="s">
+      <c r="B20" s="1"/>
+      <c r="C20" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D19" s="1">
+      <c r="D20" s="1">
         <v>1</v>
       </c>
-      <c r="E19" s="1">
+      <c r="E20" s="1">
         <v>2</v>
       </c>
-      <c r="F19" s="1">
+      <c r="F20" s="1">
         <v>3</v>
       </c>
-      <c r="G19" s="1">
+      <c r="G20" s="1">
         <v>4</v>
       </c>
-      <c r="H19" s="1">
+      <c r="H20" s="1">
         <v>5</v>
       </c>
-      <c r="I19" s="1">
+      <c r="I20" s="1">
         <v>6</v>
       </c>
-      <c r="J19" s="1">
+      <c r="J20" s="1">
         <v>7</v>
       </c>
-      <c r="K19" s="1">
-        <v>8</v>
-      </c>
-      <c r="L19" s="1">
+      <c r="K20" s="1">
+        <v>8</v>
+      </c>
+      <c r="L20" s="1">
         <v>9</v>
       </c>
-      <c r="M19" s="1">
+      <c r="M20" s="1">
         <v>10</v>
       </c>
-      <c r="N19" s="1">
+      <c r="N20" s="1">
         <v>11</v>
       </c>
-      <c r="O19" s="1">
+      <c r="O20" s="1">
         <v>12</v>
       </c>
-      <c r="P19" s="1">
+      <c r="P20" s="1">
         <v>13</v>
       </c>
-      <c r="Q19" s="1">
+      <c r="Q20" s="1">
         <v>14</v>
       </c>
-      <c r="R19" s="1">
+      <c r="R20" s="1">
         <v>15</v>
       </c>
-      <c r="S19" s="1">
+      <c r="S20" s="1">
         <v>16</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="5">
-        <v>1</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="J20" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="K20" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="L20" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="M20" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="N20" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="O20" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="P20" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q20" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="R20" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="S20" s="2" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>8</v>
@@ -2409,60 +2418,178 @@
     </row>
     <row r="22">
       <c r="A22" s="5">
+        <v>2</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S22" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5">
         <v>3</v>
       </c>
-      <c r="B22" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="J22" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="K22" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="L22" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="M22" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="N22" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="O22" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="P22" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q22" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="R22" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="S22" s="2" t="s">
+      <c r="B23" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S23" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5">
+        <v>4</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S24" s="2" t="s">
         <v>8</v>
       </c>
     </row>
@@ -2478,8 +2605,8 @@
     <mergeCell ref="A9:B9"/>
     <mergeCell ref="C9:S9"/>
     <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A20:B20"/>
   </mergeCells>
 </worksheet>
 </file>
@@ -2504,56 +2631,56 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C3" s="6"/>
       <c r="D3" s="6"/>
@@ -2572,25 +2699,25 @@
         <v>8</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F4" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="H4" s="16" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="I4" s="7" t="s">
         <v>8</v>
@@ -2613,25 +2740,25 @@
         <v>8</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D5" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E5" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="G5" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="F5" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="G5" s="8" t="s">
-        <v>66</v>
-      </c>
       <c r="H5" s="16" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="I5" s="8" t="s">
         <v>8</v>
@@ -2654,25 +2781,25 @@
         <v>8</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="F6" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="H6" s="16" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="I6" s="7" t="s">
         <v>8</v>
@@ -2695,25 +2822,25 @@
         <v>8</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D7" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="F7" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="H7" s="16" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="I7" s="8" t="s">
         <v>8</v>
@@ -2736,25 +2863,25 @@
         <v>8</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="F8" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="H8" s="16" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="I8" s="7" t="s">
         <v>8</v>
@@ -2777,25 +2904,25 @@
         <v>8</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D9" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="F9" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="H9" s="16" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="I9" s="8" t="s">
         <v>8</v>
@@ -2818,25 +2945,25 @@
         <v>8</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D10" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="F10" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="H10" s="16" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="I10" s="7" t="s">
         <v>8</v>
@@ -2859,25 +2986,25 @@
         <v>8</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D11" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="F11" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="H11" s="16" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="I11" s="8" t="s">
         <v>8</v>
@@ -2900,25 +3027,25 @@
         <v>8</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="F12" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="H12" s="16" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="I12" s="7" t="s">
         <v>8</v>
@@ -2941,25 +3068,25 @@
         <v>8</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D13" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="F13" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="H13" s="16" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="I13" s="8" t="s">
         <v>8</v>
@@ -2982,25 +3109,25 @@
         <v>8</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D14" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F14" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="H14" s="16" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="I14" s="7" t="s">
         <v>8</v>
@@ -3023,25 +3150,25 @@
         <v>8</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D15" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="F15" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="H15" s="16" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="I15" s="8" t="s">
         <v>8</v>
@@ -3064,25 +3191,25 @@
         <v>8</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D16" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="F16" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="H16" s="16" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="I16" s="7" t="s">
         <v>8</v>
@@ -3105,25 +3232,25 @@
         <v>8</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D17" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="F17" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="H17" s="16" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="I17" s="8" t="s">
         <v>8</v>
@@ -3146,25 +3273,25 @@
         <v>8</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D18" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="F18" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="H18" s="16" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="I18" s="7" t="s">
         <v>8</v>
@@ -3187,25 +3314,25 @@
         <v>8</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D19" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="F19" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="H19" s="16" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="I19" s="8" t="s">
         <v>8</v>
@@ -3228,25 +3355,25 @@
         <v>8</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D20" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="F20" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="H20" s="16" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="I20" s="7" t="s">
         <v>8</v>
@@ -3269,25 +3396,25 @@
         <v>8</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D21" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="F21" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="H21" s="16" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="I21" s="8" t="s">
         <v>8</v>
@@ -3310,25 +3437,25 @@
         <v>8</v>
       </c>
       <c r="B22" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="C22" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E22" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="C22" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="D22" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E22" s="7" t="s">
-        <v>117</v>
-      </c>
       <c r="F22" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="H22" s="16" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="I22" s="7" t="s">
         <v>8</v>
@@ -3351,25 +3478,25 @@
         <v>8</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D23" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="F23" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="H23" s="16" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="I23" s="8" t="s">
         <v>8</v>
@@ -3392,25 +3519,25 @@
         <v>8</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D24" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="F24" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G24" s="7" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="H24" s="16" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="I24" s="7" t="s">
         <v>8</v>
@@ -3433,25 +3560,25 @@
         <v>8</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D25" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="F25" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G25" s="8" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="H25" s="16" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="I25" s="8" t="s">
         <v>8</v>
@@ -3474,25 +3601,25 @@
         <v>8</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D26" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="F26" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G26" s="7" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="H26" s="16" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="I26" s="7" t="s">
         <v>8</v>
@@ -3515,25 +3642,25 @@
         <v>8</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D27" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="F27" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G27" s="8" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="H27" s="16" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="I27" s="8" t="s">
         <v>8</v>

--- a/sampleprojects/TaxReturn/excel/states/MD.xlsx
+++ b/sampleprojects/TaxReturn/excel/states/MD.xlsx
@@ -8,14 +8,15 @@
   </bookViews>
   <sheets>
     <sheet name="MD Tax" sheetId="2" r:id="rId4"/>
-    <sheet name="EDD" sheetId="3" r:id="rId6"/>
+    <sheet name="MD Military Retirement Subtract" sheetId="3" r:id="rId6"/>
+    <sheet name="EDD" sheetId="4" r:id="rId7"/>
   </sheets>
   <calcPr calcId="122211"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="138">
   <si>
     <t>DT: MD Tax</t>
   </si>
@@ -44,7 +45,7 @@
     <t/>
   </si>
   <si>
-    <t>set result.computed_state_tax = 0; set result.computed_state_taxable_income = 0; add "  Maryland Tax Calculation (top marginal 5.75%)" to job.audit_trail</t>
+    <t>set result.computed_state_tax = 0; set result.computed_state_taxable_income = 0; add "  Maryland Tax Calculation (top marginal 5.75%)" to job.audit_trail; set result.md_military_retirement_subtraction = 0.0; perform MD_Military_Retirement_Subtraction; add "  MD Form 502SU code u military retirement subtraction: $" + result.md_military_retirement_subtraction to job.audit_trail</t>
   </si>
   <si>
     <t>CONDITIONS: COMMENTS</t>
@@ -83,7 +84,7 @@
     <t>MFJ/QSS: $5,150 std ded, 5.75%</t>
   </si>
   <si>
-    <t>set result.computed_state_taxable_income = the maximum of (result.state_calc_agi - 5150.0) and 0.0; set result.computed_state_tax = result.computed_state_taxable_income * 0.0575</t>
+    <t>set result.computed_state_taxable_income = the maximum of (result.state_calc_agi - result.md_military_retirement_subtraction - 5150.0) and 0.0; set result.computed_state_tax = result.computed_state_taxable_income * 0.0575</t>
   </si>
   <si>
     <t>X</t>
@@ -92,7 +93,7 @@
     <t>HOH: $2,550 std ded, 5.75%</t>
   </si>
   <si>
-    <t>set result.computed_state_taxable_income = the maximum of (result.state_calc_agi - 2550.0) and 0.0; set result.computed_state_tax = result.computed_state_taxable_income * 0.0575</t>
+    <t>set result.computed_state_taxable_income = the maximum of (result.state_calc_agi - result.md_military_retirement_subtraction - 2550.0) and 0.0; set result.computed_state_tax = result.computed_state_taxable_income * 0.0575</t>
   </si>
   <si>
     <t>Default (Single/MFS): $2,550 std ded, 5.75%</t>
@@ -113,6 +114,60 @@
     <t>MD Single/MFS: 5.75% x max(AGI - $2,550, 0) per Md. Code, Tax-Gen. § 10-105</t>
   </si>
   <si>
+    <t>DT: MD Military Retirement Subtraction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COMMENTS: </t>
+  </si>
+  <si>
+    <t>TABLE_NUMBER: 52413</t>
+  </si>
+  <si>
+    <t>for all taxpayers</t>
+  </si>
+  <si>
+    <t>The taxpayer has military retirement income</t>
+  </si>
+  <si>
+    <t>taxpayer.military_retirement_pay &gt; 0</t>
+  </si>
+  <si>
+    <t>At least 55 on the last day of the taxable year</t>
+  </si>
+  <si>
+    <t>job.tax_year - (get yearof taxpayer.date_of_birth) &gt;= 55</t>
+  </si>
+  <si>
+    <t>Full-year resident entry only. A part-year or nonresident entry's income is built from the income entities, so the pension is not in it, and 4 U.S.C. 114 bars a state from taxing a nonresident's retirement income (#1330 review).</t>
+  </si>
+  <si>
+    <t>result.state_calc_resident_status is equal to "full_year"</t>
+  </si>
+  <si>
+    <t>Form 502SU code u: up to $20,000 at 55 and over</t>
+  </si>
+  <si>
+    <t>add the minimum of taxpayer.military_retirement_pay and md_military_retirement_exemption_55_plus to result.md_military_retirement_subtraction</t>
+  </si>
+  <si>
+    <t>Form 502SU code u: up to $12,500 under 55</t>
+  </si>
+  <si>
+    <t>add the minimum of taxpayer.military_retirement_pay and md_military_retirement_exemption_under_55 to result.md_military_retirement_subtraction</t>
+  </si>
+  <si>
+    <t>Military retirement income subtraction, Form 502SU code u: up to $20,000 for an individual at least 55 on the last day of the year (2025 Resident Booklet, Instruction 13; Tax-General 10-207(q)).</t>
+  </si>
+  <si>
+    <t>Form 502SU code u: up to $12,500 for an individual under 55.</t>
+  </si>
+  <si>
+    <t>No military retirement income for this taxpayer.</t>
+  </si>
+  <si>
+    <t>Not a full-year resident entry: the pension is not in this entry's sourced income (the roster builds it from the income entities) and 4 U.S.C. 114 bars taxing a nonresident's retirement income, so nothing is subtracted.</t>
+  </si>
+  <si>
     <t>EDD: EDD</t>
   </si>
   <si>
@@ -158,7 +213,7 @@
     <t>result</t>
   </si>
   <si>
-    <t>(23 attributes)</t>
+    <t>(24 attributes)</t>
   </si>
   <si>
     <t>md_bracket_1_limit</t>
@@ -308,7 +363,7 @@
     <t>20000.0</t>
   </si>
   <si>
-    <t>MD military retirement exemption amount for age 55+ (2025). Source: MOAA State Report Card</t>
+    <t>MD Form 502SU code u cap for an individual at least 55 years of age on the last day of the taxable year: $20,000 (2025 Resident Booklet, Instruction 13).</t>
   </si>
   <si>
     <t>md_military_retirement_exemption_under_55</t>
@@ -317,13 +372,22 @@
     <t>12500.0</t>
   </si>
   <si>
-    <t>MD military retirement exemption amount for under age 55 (2025). Source: MOAA State Report Card</t>
+    <t>MD Form 502SU code u cap for an individual under 55 on the last day of the taxable year: $12,500 (2025 Resident Booklet, Instruction 13).</t>
+  </si>
+  <si>
+    <t>md_military_retirement_subtraction</t>
+  </si>
+  <si>
+    <t>0.0</t>
+  </si>
+  <si>
+    <t>rw</t>
+  </si>
+  <si>
+    <t>Maryland Form 502SU code u, military retirement income: up to $20,000 for an individual at least 55 on the last day of the year, up to $12,500 under 55 (2025 Resident Booklet, Instruction 13). Computed per taxpayer by MD_Military_Retirement_Subtraction (#1330).</t>
   </si>
   <si>
     <t>md_military_retirement_taxable</t>
-  </si>
-  <si>
-    <t>0.0</t>
   </si>
   <si>
     <t>MD taxable military retirement after exemption (computed)</t>
@@ -1653,6 +1717,904 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
   <cols>
+    <col customWidth="true" max="1" min="1" width="20"/>
+    <col customWidth="true" max="3" min="2" width="40"/>
+    <col customWidth="true" max="19" min="4" width="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
+      <c r="O1" s="2"/>
+      <c r="P1" s="2"/>
+      <c r="Q1" s="2"/>
+      <c r="R1" s="2"/>
+      <c r="S1" s="2"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
+      <c r="O2" s="3"/>
+      <c r="P2" s="3"/>
+      <c r="Q2" s="3"/>
+      <c r="R2" s="3"/>
+      <c r="S2" s="3"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2"/>
+      <c r="N3" s="2"/>
+      <c r="O3" s="2"/>
+      <c r="P3" s="2"/>
+      <c r="Q3" s="2"/>
+      <c r="R3" s="2"/>
+      <c r="S3" s="2"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2"/>
+      <c r="N4" s="2"/>
+      <c r="O4" s="2"/>
+      <c r="P4" s="2"/>
+      <c r="Q4" s="2"/>
+      <c r="R4" s="2"/>
+      <c r="S4" s="2"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
+      <c r="N6" s="1"/>
+      <c r="O6" s="1"/>
+      <c r="P6" s="1"/>
+      <c r="Q6" s="1"/>
+      <c r="R6" s="1"/>
+      <c r="S6" s="1"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="5">
+        <v>1</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="3"/>
+      <c r="K7" s="3"/>
+      <c r="L7" s="3"/>
+      <c r="M7" s="3"/>
+      <c r="N7" s="3"/>
+      <c r="O7" s="3"/>
+      <c r="P7" s="3"/>
+      <c r="Q7" s="3"/>
+      <c r="R7" s="3"/>
+      <c r="S7" s="3"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1"/>
+      <c r="J9" s="1"/>
+      <c r="K9" s="1"/>
+      <c r="L9" s="1"/>
+      <c r="M9" s="1"/>
+      <c r="N9" s="1"/>
+      <c r="O9" s="1"/>
+      <c r="P9" s="1"/>
+      <c r="Q9" s="1"/>
+      <c r="R9" s="1"/>
+      <c r="S9" s="1"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D11" s="1">
+        <v>1</v>
+      </c>
+      <c r="E11" s="1">
+        <v>2</v>
+      </c>
+      <c r="F11" s="1">
+        <v>3</v>
+      </c>
+      <c r="G11" s="1">
+        <v>4</v>
+      </c>
+      <c r="H11" s="1">
+        <v>5</v>
+      </c>
+      <c r="I11" s="1">
+        <v>6</v>
+      </c>
+      <c r="J11" s="1">
+        <v>7</v>
+      </c>
+      <c r="K11" s="1">
+        <v>8</v>
+      </c>
+      <c r="L11" s="1">
+        <v>9</v>
+      </c>
+      <c r="M11" s="1">
+        <v>10</v>
+      </c>
+      <c r="N11" s="1">
+        <v>11</v>
+      </c>
+      <c r="O11" s="1">
+        <v>12</v>
+      </c>
+      <c r="P11" s="1">
+        <v>13</v>
+      </c>
+      <c r="Q11" s="1">
+        <v>14</v>
+      </c>
+      <c r="R11" s="1">
+        <v>15</v>
+      </c>
+      <c r="S11" s="1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5">
+        <v>1</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S12" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5">
+        <v>2</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S13" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5">
+        <v>3</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S14" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B16" s="1"/>
+      <c r="C16" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D16" s="4">
+        <v>1</v>
+      </c>
+      <c r="E16" s="4">
+        <v>2</v>
+      </c>
+      <c r="F16" s="4">
+        <v>3</v>
+      </c>
+      <c r="G16" s="4">
+        <v>4</v>
+      </c>
+      <c r="H16" s="4">
+        <v>5</v>
+      </c>
+      <c r="I16" s="4">
+        <v>6</v>
+      </c>
+      <c r="J16" s="4">
+        <v>7</v>
+      </c>
+      <c r="K16" s="4">
+        <v>8</v>
+      </c>
+      <c r="L16" s="4">
+        <v>9</v>
+      </c>
+      <c r="M16" s="4">
+        <v>10</v>
+      </c>
+      <c r="N16" s="4">
+        <v>11</v>
+      </c>
+      <c r="O16" s="4">
+        <v>12</v>
+      </c>
+      <c r="P16" s="4">
+        <v>13</v>
+      </c>
+      <c r="Q16" s="4">
+        <v>14</v>
+      </c>
+      <c r="R16" s="4">
+        <v>15</v>
+      </c>
+      <c r="S16" s="4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5">
+        <v>1</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S17" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5">
+        <v>2</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S18" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B20" s="1"/>
+      <c r="C20" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D20" s="1">
+        <v>1</v>
+      </c>
+      <c r="E20" s="1">
+        <v>2</v>
+      </c>
+      <c r="F20" s="1">
+        <v>3</v>
+      </c>
+      <c r="G20" s="1">
+        <v>4</v>
+      </c>
+      <c r="H20" s="1">
+        <v>5</v>
+      </c>
+      <c r="I20" s="1">
+        <v>6</v>
+      </c>
+      <c r="J20" s="1">
+        <v>7</v>
+      </c>
+      <c r="K20" s="1">
+        <v>8</v>
+      </c>
+      <c r="L20" s="1">
+        <v>9</v>
+      </c>
+      <c r="M20" s="1">
+        <v>10</v>
+      </c>
+      <c r="N20" s="1">
+        <v>11</v>
+      </c>
+      <c r="O20" s="1">
+        <v>12</v>
+      </c>
+      <c r="P20" s="1">
+        <v>13</v>
+      </c>
+      <c r="Q20" s="1">
+        <v>14</v>
+      </c>
+      <c r="R20" s="1">
+        <v>15</v>
+      </c>
+      <c r="S20" s="1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5">
+        <v>1</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S21" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5">
+        <v>2</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S22" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5">
+        <v>3</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S23" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5">
+        <v>4</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S24" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="12">
+    <mergeCell ref="A1:S1"/>
+    <mergeCell ref="A2:S2"/>
+    <mergeCell ref="A3:S3"/>
+    <mergeCell ref="A4:S4"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C6:S6"/>
+    <mergeCell ref="C7:S7"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="C9:S9"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A20:B20"/>
+  </mergeCells>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <cols>
     <col customWidth="true" max="1" min="1" width="18"/>
     <col customWidth="true" max="2" min="2" width="25"/>
     <col customWidth="true" max="3" min="3" width="10"/>
@@ -1669,56 +2631,56 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>41</v>
+        <v>59</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>45</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="s">
-        <v>46</v>
+        <v>64</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>47</v>
+        <v>65</v>
       </c>
       <c r="C3" s="6"/>
       <c r="D3" s="6"/>
@@ -1737,25 +2699,25 @@
         <v>8</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>49</v>
+        <v>67</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="F4" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="H4" s="16" t="s">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="I4" s="7" t="s">
         <v>8</v>
@@ -1778,25 +2740,25 @@
         <v>8</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>49</v>
+        <v>67</v>
       </c>
       <c r="D5" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="F5" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="H5" s="16" t="s">
-        <v>55</v>
+        <v>73</v>
       </c>
       <c r="I5" s="8" t="s">
         <v>8</v>
@@ -1819,25 +2781,25 @@
         <v>8</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>49</v>
+        <v>67</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="F6" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="H6" s="16" t="s">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="I6" s="7" t="s">
         <v>8</v>
@@ -1860,25 +2822,25 @@
         <v>8</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>49</v>
+        <v>67</v>
       </c>
       <c r="D7" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="F7" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="H7" s="16" t="s">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="I7" s="8" t="s">
         <v>8</v>
@@ -1901,25 +2863,25 @@
         <v>8</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>49</v>
+        <v>67</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>63</v>
+        <v>81</v>
       </c>
       <c r="F8" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="H8" s="16" t="s">
-        <v>64</v>
+        <v>82</v>
       </c>
       <c r="I8" s="7" t="s">
         <v>8</v>
@@ -1942,25 +2904,25 @@
         <v>8</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>49</v>
+        <v>67</v>
       </c>
       <c r="D9" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>66</v>
+        <v>84</v>
       </c>
       <c r="F9" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="H9" s="16" t="s">
-        <v>67</v>
+        <v>85</v>
       </c>
       <c r="I9" s="8" t="s">
         <v>8</v>
@@ -1983,25 +2945,25 @@
         <v>8</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>68</v>
+        <v>86</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>49</v>
+        <v>67</v>
       </c>
       <c r="D10" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E10" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="G10" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="F10" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="G10" s="7" t="s">
-        <v>51</v>
-      </c>
       <c r="H10" s="16" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="I10" s="7" t="s">
         <v>8</v>
@@ -2024,25 +2986,25 @@
         <v>8</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>49</v>
+        <v>67</v>
       </c>
       <c r="D11" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="F11" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="H11" s="16" t="s">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="I11" s="8" t="s">
         <v>8</v>
@@ -2065,25 +3027,25 @@
         <v>8</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>49</v>
+        <v>67</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="F12" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="H12" s="16" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="I12" s="7" t="s">
         <v>8</v>
@@ -2106,25 +3068,25 @@
         <v>8</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>49</v>
+        <v>67</v>
       </c>
       <c r="D13" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="F13" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="H13" s="16" t="s">
-        <v>79</v>
+        <v>97</v>
       </c>
       <c r="I13" s="8" t="s">
         <v>8</v>
@@ -2147,25 +3109,25 @@
         <v>8</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>49</v>
+        <v>67</v>
       </c>
       <c r="D14" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>81</v>
+        <v>99</v>
       </c>
       <c r="F14" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="H14" s="16" t="s">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="I14" s="7" t="s">
         <v>8</v>
@@ -2188,25 +3150,25 @@
         <v>8</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>83</v>
+        <v>101</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>49</v>
+        <v>67</v>
       </c>
       <c r="D15" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>84</v>
+        <v>102</v>
       </c>
       <c r="F15" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="H15" s="16" t="s">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="I15" s="8" t="s">
         <v>8</v>
@@ -2229,25 +3191,25 @@
         <v>8</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>49</v>
+        <v>67</v>
       </c>
       <c r="D16" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="F16" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="H16" s="16" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="I16" s="7" t="s">
         <v>8</v>
@@ -2270,25 +3232,25 @@
         <v>8</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>89</v>
+        <v>107</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>49</v>
+        <v>67</v>
       </c>
       <c r="D17" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>90</v>
+        <v>108</v>
       </c>
       <c r="F17" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="H17" s="16" t="s">
-        <v>91</v>
+        <v>109</v>
       </c>
       <c r="I17" s="8" t="s">
         <v>8</v>
@@ -2311,25 +3273,25 @@
         <v>8</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>92</v>
+        <v>110</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>49</v>
+        <v>67</v>
       </c>
       <c r="D18" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>93</v>
+        <v>111</v>
       </c>
       <c r="F18" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="H18" s="16" t="s">
-        <v>94</v>
+        <v>112</v>
       </c>
       <c r="I18" s="7" t="s">
         <v>8</v>
@@ -2352,25 +3314,25 @@
         <v>8</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>95</v>
+        <v>113</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>49</v>
+        <v>67</v>
       </c>
       <c r="D19" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>96</v>
+        <v>114</v>
       </c>
       <c r="F19" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="H19" s="16" t="s">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="I19" s="8" t="s">
         <v>8</v>
@@ -2393,25 +3355,25 @@
         <v>8</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>98</v>
+        <v>116</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>49</v>
+        <v>67</v>
       </c>
       <c r="D20" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>99</v>
+        <v>117</v>
       </c>
       <c r="F20" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="H20" s="16" t="s">
-        <v>100</v>
+        <v>118</v>
       </c>
       <c r="I20" s="7" t="s">
         <v>8</v>
@@ -2434,25 +3396,25 @@
         <v>8</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>49</v>
+        <v>67</v>
       </c>
       <c r="D21" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>102</v>
+        <v>120</v>
       </c>
       <c r="F21" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>51</v>
+        <v>121</v>
       </c>
       <c r="H21" s="16" t="s">
-        <v>103</v>
+        <v>122</v>
       </c>
       <c r="I21" s="8" t="s">
         <v>8</v>
@@ -2475,25 +3437,25 @@
         <v>8</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>104</v>
+        <v>123</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>49</v>
+        <v>67</v>
       </c>
       <c r="D22" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>105</v>
+        <v>120</v>
       </c>
       <c r="F22" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="H22" s="16" t="s">
-        <v>106</v>
+        <v>124</v>
       </c>
       <c r="I22" s="7" t="s">
         <v>8</v>
@@ -2516,25 +3478,25 @@
         <v>8</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>107</v>
+        <v>125</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>49</v>
+        <v>67</v>
       </c>
       <c r="D23" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>108</v>
+        <v>126</v>
       </c>
       <c r="F23" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="H23" s="16" t="s">
-        <v>109</v>
+        <v>127</v>
       </c>
       <c r="I23" s="8" t="s">
         <v>8</v>
@@ -2557,25 +3519,25 @@
         <v>8</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>110</v>
+        <v>128</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>49</v>
+        <v>67</v>
       </c>
       <c r="D24" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>111</v>
+        <v>129</v>
       </c>
       <c r="F24" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G24" s="7" t="s">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="H24" s="16" t="s">
-        <v>112</v>
+        <v>130</v>
       </c>
       <c r="I24" s="7" t="s">
         <v>8</v>
@@ -2598,25 +3560,25 @@
         <v>8</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>113</v>
+        <v>131</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>49</v>
+        <v>67</v>
       </c>
       <c r="D25" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>108</v>
+        <v>132</v>
       </c>
       <c r="F25" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G25" s="8" t="s">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="H25" s="16" t="s">
-        <v>114</v>
+        <v>133</v>
       </c>
       <c r="I25" s="8" t="s">
         <v>8</v>
@@ -2639,25 +3601,25 @@
         <v>8</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>115</v>
+        <v>134</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>49</v>
+        <v>67</v>
       </c>
       <c r="D26" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>108</v>
+        <v>129</v>
       </c>
       <c r="F26" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G26" s="7" t="s">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="H26" s="16" t="s">
-        <v>116</v>
+        <v>135</v>
       </c>
       <c r="I26" s="7" t="s">
         <v>8</v>
@@ -2672,6 +3634,47 @@
         <v>8</v>
       </c>
       <c r="M26" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B27" s="9" t="s">
+        <v>136</v>
+      </c>
+      <c r="C27" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="D27" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E27" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="F27" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="G27" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="H27" s="16" t="s">
+        <v>137</v>
+      </c>
+      <c r="I27" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="J27" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="K27" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="L27" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="M27" s="8" t="s">
         <v>8</v>
       </c>
     </row>
